--- a/data/trans_camb/IP1002-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1002-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 9,56</t>
+          <t>-1,35; 9,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 3,94</t>
+          <t>-4,08; 3,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 0,0</t>
+          <t>-6,71; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,26</t>
+          <t>0,0; 6,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,74</t>
+          <t>0,0; 6,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,76</t>
+          <t>0,0; 6,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 6,37</t>
+          <t>0,13; 5,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 3,61</t>
+          <t>-1,25; 3,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 1,11</t>
+          <t>-2,47; 1,08</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 4,78</t>
+          <t>-0,61; 4,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 1,22</t>
+          <t>-1,85; 1,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 2,43</t>
+          <t>-1,25; 2,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 2,28</t>
+          <t>-3,52; 2,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 4,06</t>
+          <t>-2,66; 4,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 0,38</t>
+          <t>-5,01; 0,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,68</t>
+          <t>-1,21; 2,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 2,26</t>
+          <t>-1,61; 2,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 0,62</t>
+          <t>-2,63; 0,65</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-82,11; 670,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-62,74; 638,89</t>
+          <t>-66,07; 558,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-79,68; 516,05</t>
+          <t>-75,17; 509,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,33</t>
+          <t>0,0; 7,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,93</t>
+          <t>0,0; 5,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,2</t>
+          <t>0,0; 5,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 7,75</t>
+          <t>0,91; 7,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,62</t>
+          <t>0,98; 5,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,87</t>
+          <t>0,0; 2,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,87</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,37; -0,7</t>
+          <t>-7,36; -0,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 1,08</t>
+          <t>-5,57; 1,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 3,51</t>
+          <t>-4,7; 4,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 5,4</t>
+          <t>-2,06; 5,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 1,55</t>
+          <t>-3,44; 1,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 0,0</t>
+          <t>-5,16; 0,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 1,9</t>
+          <t>-2,92; 1,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 0,98</t>
+          <t>-3,65; 1,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 1,23</t>
+          <t>-3,22; 1,39</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 655,25</t>
+          <t>-100,0; 355,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 4,01</t>
+          <t>-8,48; 3,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 4,38</t>
+          <t>-8,97; 3,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-11,94; -1,44</t>
+          <t>-10,66; -1,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,93; 20,23</t>
+          <t>2,7; 18,77</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 0,0</t>
+          <t>-8,3; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 0,0</t>
+          <t>-8,11; 0,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 9,19</t>
+          <t>-0,96; 9,66</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 1,38</t>
+          <t>-6,04; 1,27</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,42; -0,73</t>
+          <t>-7,39; -0,73</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-40,27; 923,09</t>
+          <t>-42,17; 1004,25</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1694,7 +1694,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 3,95</t>
+          <t>-2,6; 3,97</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 2,29</t>
+          <t>-5,01; 2,3</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 0,0</t>
+          <t>-6,38; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,17; 10,01</t>
+          <t>1,18; 9,92</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,27</t>
+          <t>0,0; 9,59</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,52</t>
+          <t>0,0; 5,47</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 5,43</t>
+          <t>-0,0; 5,61</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,01</t>
+          <t>-1,24; 3,06</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,19</t>
+          <t>-2,44; 1,18</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 3,35</t>
+          <t>-0,57; 3,78</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 1,73</t>
+          <t>-1,05; 1,74</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,55</t>
+          <t>0,94; 7,12</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 3,57</t>
+          <t>-0,68; 3,38</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,9</t>
+          <t>-1,21; 2,21</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,59; 9,42</t>
+          <t>1,85; 10,45</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 2,87</t>
+          <t>-0,12; 2,79</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,52</t>
+          <t>-1,04; 1,25</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,19; 7,43</t>
+          <t>1,99; 7,2</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-56,5; —</t>
+          <t>-52,26; —</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>101,75; —</t>
+          <t>95,02; —</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,09; -0,75</t>
+          <t>-4,32; -0,68</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 1,6</t>
+          <t>-2,58; 1,66</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 1,46</t>
+          <t>-3,46; 1,26</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 0,16</t>
+          <t>-4,14; 0,21</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 2,01</t>
+          <t>-3,32; 1,98</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,91; -0,85</t>
+          <t>-5,17; -0,86</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,52; -0,67</t>
+          <t>-3,51; -0,6</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 1,36</t>
+          <t>-2,1; 1,06</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,53; -0,43</t>
+          <t>-3,31; -0,41</t>
         </is>
       </c>
     </row>
@@ -2300,22 +2300,22 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-89,81; 340,15</t>
+          <t>-86,3; 313,45</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 275,73</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 151,41</t>
+          <t>-100,0; 162,9</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-80,16; 206,27</t>
+          <t>-84,51; 229,59</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -20,33</t>
+          <t>-100,0; -15,17</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-69,41; 109,39</t>
+          <t>-69,87; 87,17</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 14,33</t>
+          <t>-100,0; 22,01</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,26</t>
+          <t>-1,0; 1,14</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,67</t>
+          <t>-1,23; 0,64</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,05</t>
+          <t>-1,12; 0,92</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,33</t>
+          <t>0,22; 2,51</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,17</t>
+          <t>-0,73; 1,07</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,4</t>
+          <t>-0,78; 1,37</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,48</t>
+          <t>-0,03; 1,51</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,69</t>
+          <t>-0,73; 0,62</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,83</t>
+          <t>-0,69; 0,76</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-47,55; 143,43</t>
+          <t>-50,81; 117,38</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-64,08; 89,53</t>
+          <t>-65,32; 77,94</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-59,44; 121,12</t>
+          <t>-58,81; 93,71</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 333,44</t>
+          <t>4,84; 352,55</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-46,01; 153,93</t>
+          <t>-46,48; 146,55</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-52,63; 175,68</t>
+          <t>-51,33; 179,78</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 165,65</t>
+          <t>-5,32; 157,97</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-43,99; 71,46</t>
+          <t>-44,43; 64,01</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-42,61; 86,84</t>
+          <t>-42,23; 79,44</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1002-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1002-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 9,87</t>
+          <t>-0,91; 10,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 3,62</t>
+          <t>-3,09; 3,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 0,0</t>
+          <t>-8,15; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,78</t>
+          <t>0,0; 8,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,09</t>
+          <t>0,0; 6,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,29</t>
+          <t>0,0; 5,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 5,76</t>
+          <t>-0,06; 6,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,18</t>
+          <t>-1,23; 3,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 1,08</t>
+          <t>-1,98; 1,11</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 4,88</t>
+          <t>-0,61; 4,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,78</t>
+          <t>-1,86; 1,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 2,52</t>
+          <t>-1,24; 2,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 2,31</t>
+          <t>-3,61; 2,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 4,12</t>
+          <t>-2,69; 4,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 0,43</t>
+          <t>-4,82; 0,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,78</t>
+          <t>-1,29; 2,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 2,24</t>
+          <t>-1,4; 2,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 0,65</t>
+          <t>-2,48; 0,65</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,74; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-66,07; 558,74</t>
+          <t>-64,78; 576,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-75,17; 509,52</t>
+          <t>-69,99; 526,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,25</t>
+          <t>0,0; 6,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,29</t>
+          <t>0,0; 5,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,95</t>
+          <t>0,0; 5,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 7,69</t>
+          <t>0,91; 8,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,57</t>
+          <t>0,96; 5,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,35</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,9</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,36; -0,7</t>
+          <t>-7,9; -0,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 1,32</t>
+          <t>-6,18; 1,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 4,01</t>
+          <t>-5,16; 3,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 5,34</t>
+          <t>-2,03; 5,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 1,56</t>
+          <t>-4,08; 1,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 0,0</t>
+          <t>-5,97; 0,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 1,69</t>
+          <t>-2,93; 1,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 1,01</t>
+          <t>-3,25; 0,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 1,39</t>
+          <t>-3,25; 1,43</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 355,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 306,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 3,01</t>
+          <t>-8,95; 3,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 3,43</t>
+          <t>-8,91; 4,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,66; -1,46</t>
+          <t>-11,91; -1,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,7; 18,77</t>
+          <t>2,36; 20,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 0,0</t>
+          <t>-7,41; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 0,0</t>
+          <t>-8,15; 0,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 9,66</t>
+          <t>-1,31; 9,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 1,27</t>
+          <t>-5,77; 1,26</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,39; -0,73</t>
+          <t>-6,94; -0,72</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-42,17; 1004,25</t>
+          <t>-47,77; 933,49</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 3,97</t>
+          <t>-2,55; 4,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 2,3</t>
+          <t>-3,95; 2,3</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 0,0</t>
+          <t>-5,63; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,18; 9,92</t>
+          <t>1,16; 10,06</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,59</t>
+          <t>0,0; 6,65</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,47</t>
+          <t>0,0; 5,54</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 5,61</t>
+          <t>-0,55; 5,39</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 3,06</t>
+          <t>-1,23; 2,93</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 1,18</t>
+          <t>-2,0; 1,2</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 3,78</t>
+          <t>-0,56; 3,81</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 1,74</t>
+          <t>-1,53; 1,7</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,94; 7,12</t>
+          <t>0,96; 7,15</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 3,38</t>
+          <t>-0,61; 3,69</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,21</t>
+          <t>-1,22; 1,9</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,85; 10,45</t>
+          <t>1,82; 9,94</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 2,79</t>
+          <t>-0,18; 2,71</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 1,25</t>
+          <t>-0,88; 1,31</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,99; 7,2</t>
+          <t>2,0; 6,88</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-52,26; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>95,02; —</t>
+          <t>68,69; —</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,32; -0,68</t>
+          <t>-4,0; -0,55</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,66</t>
+          <t>-2,95; 1,55</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 1,26</t>
+          <t>-3,04; 1,36</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 0,21</t>
+          <t>-4,27; 0,15</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 1,98</t>
+          <t>-3,36; 1,93</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-5,17; -0,86</t>
+          <t>-4,97; -0,84</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,51; -0,6</t>
+          <t>-3,56; -0,74</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,06</t>
+          <t>-2,34; 1,23</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,31; -0,41</t>
+          <t>-3,44; -0,52</t>
         </is>
       </c>
     </row>
@@ -2300,22 +2300,22 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-86,3; 313,45</t>
+          <t>-87,67; 288,78</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 275,73</t>
+          <t>-100,0; 400,52</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 162,9</t>
+          <t>-100,0; 79,2</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-84,51; 229,59</t>
+          <t>-83,4; 199,37</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -15,17</t>
+          <t>-100,0; -8,33</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-69,87; 87,17</t>
+          <t>-72,36; 107,76</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 22,01</t>
+          <t>-100,0; -6,61</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,14</t>
+          <t>-0,81; 1,22</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,64</t>
+          <t>-1,22; 0,68</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,92</t>
+          <t>-1,1; 1,0</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,51</t>
+          <t>0,08; 2,42</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,07</t>
+          <t>-0,79; 1,03</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,37</t>
+          <t>-0,77; 1,46</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 1,51</t>
+          <t>-0,09; 1,44</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,62</t>
+          <t>-0,75; 0,57</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,76</t>
+          <t>-0,7; 0,84</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-50,81; 117,38</t>
+          <t>-44,54; 139,71</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-65,32; 77,94</t>
+          <t>-64,16; 73,01</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-58,81; 93,71</t>
+          <t>-56,9; 118,48</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4,84; 352,55</t>
+          <t>-3,91; 321,08</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-46,48; 146,55</t>
+          <t>-49,93; 136,18</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-51,33; 179,78</t>
+          <t>-51,55; 205,32</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 157,97</t>
+          <t>-7,22; 143,26</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-44,43; 64,01</t>
+          <t>-44,36; 59,28</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-42,23; 79,44</t>
+          <t>-44,86; 85,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1002-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1002-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,34 +624,34 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,48</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,23</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>3,6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,55</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>-1,35</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,48</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,23</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,02</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2,47</t>
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,1</t>
+          <t>-0,02</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 10,8</t>
+          <t>0,0; 7,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 3,76</t>
+          <t>0,0; 6,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 0,0</t>
+          <t>0,0; 7,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,24</t>
+          <t>-1,35; 9,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,63</t>
+          <t>-3,14; 3,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,32</t>
+          <t>-6,7; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 6,37</t>
+          <t>0,11; 6,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 3,25</t>
+          <t>-0,83; 3,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 1,11</t>
+          <t>-1,9; 1,24</t>
         </is>
       </c>
     </row>
@@ -730,34 +730,34 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>267,76%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>40,99%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>393,63%</t>
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-15,2%</t>
+          <t>-2,55%</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,3</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,89</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-1,49</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,8</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,01</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,04</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,3</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,89</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,39</t>
+          <t>0,25</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,7</t>
+          <t>-0,66</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 4,87</t>
+          <t>-3,88; 2,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 1,23</t>
+          <t>-2,54; 4,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 2,58</t>
+          <t>-4,78; 0,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 2,32</t>
+          <t>-0,61; 4,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 4,09</t>
+          <t>-2,21; 1,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 0,42</t>
+          <t>-1,23; 3,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 2,61</t>
+          <t>-1,13; 2,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 2,4</t>
+          <t>-1,62; 2,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 0,65</t>
+          <t>-2,73; 0,71</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-14,65%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>44,08%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-74,2%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>294,91%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-1,37%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-14,65%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>44,08%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-68,94%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-52,09%</t>
+          <t>-49,04%</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-82,11; 670,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-85,74; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-64,78; 576,98</t>
+          <t>-62,74; 638,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-69,99; 526,07</t>
+          <t>-79,68; 516,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,9</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>2,07</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1,04</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,06</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,9</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,1</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,54</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,3</t>
+          <t>0,92; 7,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 8,17</t>
+          <t>0,0; 7,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,54</t>
+          <t>0,97; 5,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 2,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,9</t>
+          <t>0,0; 3,01</t>
         </is>
       </c>
     </row>
@@ -1167,27 +1167,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,58</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,26</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-1,03</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-2,57</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-1,59</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,98</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,58</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,26</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,03</t>
+          <t>-1,01</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,02</t>
+          <t>-1,01</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,9; -0,7</t>
+          <t>-1,37; 5,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 1,0</t>
+          <t>-3,78; 1,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 3,36</t>
+          <t>-4,68; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 5,13</t>
+          <t>-7,37; -0,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 1,56</t>
+          <t>-6,08; 1,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 0,0</t>
+          <t>-4,57; 3,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 1,78</t>
+          <t>-3,0; 1,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 0,95</t>
+          <t>-3,48; 0,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 1,43</t>
+          <t>-3,53; 1,29</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>154,01%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-25,1%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-61,79%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-37,97%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>154,01%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-25,1%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-39,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-57,56%</t>
+          <t>-56,58%</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 655,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 306,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>9,43</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,62</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-1,62</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-2,49</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-2,43</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>-4,48</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>9,43</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,62</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-1,62</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 3,69</t>
+          <t>1,93; 20,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 4,04</t>
+          <t>-8,1; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-11,91; -1,47</t>
+          <t>-9,05; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,36; 20,18</t>
+          <t>-8,86; 4,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 0,0</t>
+          <t>-8,92; 4,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 0,0</t>
+          <t>-11,94; -1,44</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 9,68</t>
+          <t>-1,03; 9,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 1,26</t>
+          <t>-5,84; 1,38</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,94; -0,72</t>
+          <t>-7,42; -0,73</t>
         </is>
       </c>
     </row>
@@ -1594,27 +1594,27 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>582,44%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-55,49%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-54,22%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>582,44%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-47,77; 933,49</t>
+          <t>-40,27; 923,09</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1704,34 +1704,34 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>3,72</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1,28</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0,98</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>0,03</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-0,15</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>-1,27</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>3,72</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>1,06</t>
-        </is>
-      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t>1,94</t>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>-0,11</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 4,0</t>
+          <t>1,17; 10,01</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 2,3</t>
+          <t>0,0; 7,27</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 0,0</t>
+          <t>0,0; 5,03</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,16; 10,06</t>
+          <t>-2,57; 3,95</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,65</t>
+          <t>-3,96; 2,29</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,54</t>
+          <t>-7,08; 0,0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 5,39</t>
+          <t>-0,01; 5,43</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 2,93</t>
+          <t>-1,22; 3,01</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,2</t>
+          <t>-1,91; 1,04</t>
         </is>
       </c>
     </row>
@@ -1810,34 +1810,34 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>2,45%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-11,46%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
           <t>316,32%</t>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-5,12%</t>
+          <t>-17,36%</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>1,04</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0,39</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>5,17</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>1,36</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>0,04</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>3,31</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1,04</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>0,39</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,89</t>
+          <t>3,26</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4,19</t>
+          <t>4,28</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 3,81</t>
+          <t>-0,61; 3,57</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 1,7</t>
+          <t>-1,16; 1,9</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,96; 7,15</t>
+          <t>1,61; 9,8</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 3,69</t>
+          <t>-0,58; 3,35</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,9</t>
+          <t>-1,05; 1,73</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,82; 9,94</t>
+          <t>0,73; 6,71</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 2,71</t>
+          <t>-0,1; 2,87</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,31</t>
+          <t>-0,85; 1,52</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,0; 6,88</t>
+          <t>2,24; 7,53</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>194,61%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>73,64%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>965,01%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>260,46%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>7,22%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>631,66%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>194,61%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>73,64%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>912,36%</t>
+          <t>621,72%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>790,1%</t>
+          <t>807,91%</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-56,5; —</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>68,69; —</t>
+          <t>109,2; —</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-1,75</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-0,5</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-2,48</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-1,95</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-0,56</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-0,91</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-1,75</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-0,5</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-2,48</t>
+          <t>-0,95</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,0; -0,55</t>
+          <t>-4,19; 0,16</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 1,55</t>
+          <t>-2,96; 2,01</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 1,36</t>
+          <t>-4,91; -0,85</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 0,15</t>
+          <t>-4,09; -0,75</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 1,93</t>
+          <t>-2,75; 1,6</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,97; -0,84</t>
+          <t>-3,15; 1,32</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,56; -0,74</t>
+          <t>-3,52; -0,67</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,23</t>
+          <t>-2,14; 1,36</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,44; -0,52</t>
+          <t>-3,51; -0,42</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-70,49%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-20,15%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-28,66%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-47,01%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-70,49%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-20,15%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-48,89%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-78,78%</t>
+          <t>-78,99%</t>
         </is>
       </c>
     </row>
@@ -2295,27 +2295,27 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 151,41</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-87,67; 288,78</t>
+          <t>-80,16; 206,27</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 400,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 79,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-83,4; 199,37</t>
+          <t>-89,81; 340,15</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -8,33</t>
+          <t>-100,0; -20,33</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-72,36; 107,76</t>
+          <t>-69,41; 109,39</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -6,61</t>
+          <t>-100,0; 17,62</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>1,21</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>0,17</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>0,23</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>0,12</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>-0,31</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>1,21</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,1</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,22</t>
+          <t>0,04; 2,33</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,68</t>
+          <t>-0,75; 1,17</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 1,0</t>
+          <t>-0,81; 1,34</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,08; 2,42</t>
+          <t>-0,87; 1,26</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,03</t>
+          <t>-1,21; 0,67</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 1,46</t>
+          <t>-1,06; 1,14</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 1,44</t>
+          <t>-0,06; 1,48</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,57</t>
+          <t>-0,75; 0,69</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,84</t>
+          <t>-0,66; 0,9</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>102,78%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>14,75%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>19,68%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>8,33%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>-22,18%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-7,11%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>102,78%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>14,75%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>-2,5%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-44,54; 139,71</t>
+          <t>-3,22; 333,44</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-64,16; 73,01</t>
+          <t>-46,01; 153,93</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-56,9; 118,48</t>
+          <t>-51,11; 176,99</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 321,08</t>
+          <t>-47,55; 143,43</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-49,93; 136,18</t>
+          <t>-64,08; 89,53</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-51,55; 205,32</t>
+          <t>-58,94; 130,39</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 143,26</t>
+          <t>-5,73; 165,65</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-44,36; 59,28</t>
+          <t>-43,99; 71,46</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-44,86; 85,7</t>
+          <t>-40,78; 91,79</t>
         </is>
       </c>
     </row>
